--- a/บันทึกน้ำมัน.xlsx
+++ b/บันทึกน้ำมัน.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OpenCode_Project\โพนพิสัย\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A99A58F8-6DC0-4F74-825B-3225BE8E716B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE9DCBDE-9675-40D7-9D67-95120028BC5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="28800" windowHeight="11295" xr2:uid="{7F9CD1FF-A926-4F2B-BBA6-B67202939688}"/>
+    <workbookView xWindow="2660" yWindow="2660" windowWidth="21600" windowHeight="12750" xr2:uid="{7F9CD1FF-A926-4F2B-BBA6-B67202939688}"/>
   </bookViews>
   <sheets>
     <sheet name="ผู้รับผิดชอบรถ" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="24">
   <si>
     <t>line_id</t>
   </si>
@@ -102,6 +102,15 @@
   </si>
   <si>
     <t>received_at</t>
+  </si>
+  <si>
+    <t>fuel_pct</t>
+  </si>
+  <si>
+    <t>gauge_before_url</t>
+  </si>
+  <si>
+    <t>gauge_after_url</t>
   </si>
 </sst>
 </file>
@@ -490,14 +499,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97E272C6-3B76-4443-84A3-2742D4D9AF7B}">
   <dimension ref="A1:C1"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.625" customWidth="1"/>
-    <col min="2" max="2" width="18.625" customWidth="1"/>
-    <col min="3" max="3" width="14.625" customWidth="1"/>
+    <col min="1" max="1" width="14.58203125" customWidth="1"/>
+    <col min="2" max="2" width="18.58203125" customWidth="1"/>
+    <col min="3" max="3" width="14.58203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -515,18 +524,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{615C8703-9BB5-41C6-B284-D3B89AE9D3AE}">
-  <dimension ref="A1:H1"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:I1"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="34.625" customWidth="1"/>
-    <col min="2" max="3" width="18.625" customWidth="1"/>
-    <col min="4" max="4" width="12.625" customWidth="1"/>
-    <col min="5" max="5" width="18.625" customWidth="1"/>
-    <col min="6" max="7" width="12.625" customWidth="1"/>
-    <col min="8" max="8" width="30.625" customWidth="1"/>
+    <col min="1" max="1" width="34.58203125" customWidth="1"/>
+    <col min="2" max="3" width="18.58203125" customWidth="1"/>
+    <col min="4" max="4" width="12.58203125" customWidth="1"/>
+    <col min="5" max="5" width="18.58203125" customWidth="1"/>
+    <col min="6" max="7" width="12.58203125" customWidth="1"/>
+    <col min="8" max="8" width="30.58203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -549,6 +558,9 @@
         <v>8</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1" t="s">
         <v>9</v>
       </c>
     </row>
@@ -559,20 +571,20 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10984F6D-A685-47AC-88DE-D51C22FD1FA0}">
-  <dimension ref="A1:I1"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:K1"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="34.625" customWidth="1"/>
-    <col min="2" max="3" width="14.625" customWidth="1"/>
-    <col min="4" max="4" width="12.625" customWidth="1"/>
-    <col min="5" max="5" width="14.625" customWidth="1"/>
-    <col min="6" max="6" width="12.625" customWidth="1"/>
-    <col min="7" max="7" width="14.625" customWidth="1"/>
-    <col min="8" max="8" width="60.625" customWidth="1"/>
-    <col min="9" max="9" width="30.625" customWidth="1"/>
+    <col min="1" max="1" width="34.58203125" customWidth="1"/>
+    <col min="2" max="3" width="14.58203125" customWidth="1"/>
+    <col min="4" max="4" width="12.58203125" customWidth="1"/>
+    <col min="5" max="5" width="14.58203125" customWidth="1"/>
+    <col min="6" max="6" width="12.58203125" customWidth="1"/>
+    <col min="7" max="7" width="14.58203125" customWidth="1"/>
+    <col min="8" max="8" width="60.58203125" customWidth="1"/>
+    <col min="9" max="9" width="30.58203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -599,6 +611,12 @@
       </c>
       <c r="I1" s="1" t="s">
         <v>9</v>
+      </c>
+      <c r="J1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K1" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -609,17 +627,17 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE5D9DDB-5850-4011-813E-4F8FD02F1723}">
   <dimension ref="A1:F1"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="30.625" customWidth="1"/>
-    <col min="2" max="2" width="18.625" customWidth="1"/>
-    <col min="3" max="3" width="34.625" customWidth="1"/>
-    <col min="4" max="4" width="10.625" customWidth="1"/>
-    <col min="5" max="5" width="30.625" customWidth="1"/>
-    <col min="6" max="6" width="18.625" customWidth="1"/>
+    <col min="1" max="1" width="30.58203125" customWidth="1"/>
+    <col min="2" max="2" width="18.58203125" customWidth="1"/>
+    <col min="3" max="3" width="34.58203125" customWidth="1"/>
+    <col min="4" max="4" width="10.58203125" customWidth="1"/>
+    <col min="5" max="5" width="30.58203125" customWidth="1"/>
+    <col min="6" max="6" width="18.58203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>17</v>
       </c>
